--- a/public/examples/work/journal.xlsx
+++ b/public/examples/work/journal.xlsx
@@ -70,7 +70,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="18">
   <si>
     <t>S</t>
   </si>
@@ -120,6 +120,15 @@
   </si>
   <si>
     <t>Дата здачі відомості</t>
+  </si>
+  <si>
+    <t>41</t>
+  </si>
+  <si>
+    <t>61</t>
+  </si>
+  <si>
+    <t>81</t>
   </si>
 </sst>
 </file>
@@ -279,7 +288,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -338,6 +347,9 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -886,7 +898,7 @@
       <c r="C5" s="14">
         <v>1</v>
       </c>
-      <c r="D5" s="18">
+      <c r="D5" s="20">
         <v>161</v>
       </c>
       <c r="E5" s="16"/>
@@ -1389,7 +1401,7 @@
       <c r="C5" s="14">
         <v>1</v>
       </c>
-      <c r="D5" s="18">
+      <c r="D5" s="20">
         <v>181</v>
       </c>
       <c r="E5" s="16"/>
@@ -1892,7 +1904,7 @@
       <c r="C5" s="14">
         <v>1</v>
       </c>
-      <c r="D5" s="18">
+      <c r="D5" s="20">
         <v>201</v>
       </c>
       <c r="E5" s="16"/>
@@ -2395,7 +2407,7 @@
       <c r="C5" s="14">
         <v>1</v>
       </c>
-      <c r="D5" s="18">
+      <c r="D5" s="20">
         <v>221</v>
       </c>
       <c r="E5" s="16"/>
@@ -2898,7 +2910,7 @@
       <c r="C5" s="14">
         <v>1</v>
       </c>
-      <c r="D5" s="18">
+      <c r="D5" s="20">
         <v>241</v>
       </c>
       <c r="E5" s="16"/>
@@ -3401,7 +3413,7 @@
       <c r="C5" s="14">
         <v>1</v>
       </c>
-      <c r="D5" s="18">
+      <c r="D5" s="20">
         <v>261</v>
       </c>
       <c r="E5" s="16"/>
@@ -3904,7 +3916,7 @@
       <c r="C5" s="14">
         <v>1</v>
       </c>
-      <c r="D5" s="18">
+      <c r="D5" s="20">
         <v>281</v>
       </c>
       <c r="E5" s="16"/>
@@ -4407,7 +4419,7 @@
       <c r="C5" s="14">
         <v>1</v>
       </c>
-      <c r="D5" s="18">
+      <c r="D5" s="20">
         <v>301</v>
       </c>
       <c r="E5" s="16"/>
@@ -4910,7 +4922,7 @@
       <c r="C5" s="14">
         <v>1</v>
       </c>
-      <c r="D5" s="18">
+      <c r="D5" s="20">
         <v>321</v>
       </c>
       <c r="E5" s="16"/>
@@ -5413,7 +5425,7 @@
       <c r="C5" s="14">
         <v>1</v>
       </c>
-      <c r="D5" s="18">
+      <c r="D5" s="20">
         <v>341</v>
       </c>
       <c r="E5" s="16"/>
@@ -6419,7 +6431,7 @@
       <c r="C5" s="14">
         <v>1</v>
       </c>
-      <c r="D5" s="18">
+      <c r="D5" s="20">
         <v>361</v>
       </c>
       <c r="E5" s="16"/>
@@ -6922,7 +6934,7 @@
       <c r="C5" s="14">
         <v>1</v>
       </c>
-      <c r="D5" s="18">
+      <c r="D5" s="20">
         <v>381</v>
       </c>
       <c r="E5" s="16"/>
@@ -7928,8 +7940,8 @@
       <c r="C5" s="14">
         <v>1</v>
       </c>
-      <c r="D5" s="18">
-        <v>41</v>
+      <c r="D5" s="18" t="s">
+        <v>15</v>
       </c>
       <c r="E5" s="16"/>
       <c r="F5" s="17"/>
@@ -8431,8 +8443,8 @@
       <c r="C5" s="14">
         <v>1</v>
       </c>
-      <c r="D5" s="18">
-        <v>61</v>
+      <c r="D5" s="18" t="s">
+        <v>16</v>
       </c>
       <c r="E5" s="16"/>
       <c r="F5" s="17"/>
@@ -8934,8 +8946,8 @@
       <c r="C5" s="14">
         <v>1</v>
       </c>
-      <c r="D5" s="18">
-        <v>81</v>
+      <c r="D5" s="18" t="s">
+        <v>17</v>
       </c>
       <c r="E5" s="16"/>
       <c r="F5" s="17"/>
@@ -9437,7 +9449,7 @@
       <c r="C5" s="14">
         <v>1</v>
       </c>
-      <c r="D5" s="18">
+      <c r="D5" s="20">
         <v>101</v>
       </c>
       <c r="E5" s="16"/>
@@ -9940,7 +9952,7 @@
       <c r="C5" s="14">
         <v>1</v>
       </c>
-      <c r="D5" s="18">
+      <c r="D5" s="20">
         <v>121</v>
       </c>
       <c r="E5" s="16"/>
@@ -10443,7 +10455,7 @@
       <c r="C5" s="14">
         <v>1</v>
       </c>
-      <c r="D5" s="18">
+      <c r="D5" s="20">
         <v>141</v>
       </c>
       <c r="E5" s="16"/>
